--- a/data/trans_dic/P16A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 20,91</t>
+          <t>16,62; 21,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,78; 27,66</t>
+          <t>22,02; 27,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,3; 27,23</t>
+          <t>20,97; 26,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,7; 38,39</t>
+          <t>30,89; 38,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,51; 34,51</t>
+          <t>29,69; 34,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,38; 43,75</t>
+          <t>38,08; 43,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,4; 44,97</t>
+          <t>38,33; 45,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,93; 62,44</t>
+          <t>56,92; 62,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 27,97</t>
+          <t>24,22; 27,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,08; 36,04</t>
+          <t>32,01; 36,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 36,13</t>
+          <t>31,77; 36,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,32; 51,8</t>
+          <t>47,01; 51,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,45</t>
+          <t>10,3; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 17,93</t>
+          <t>14,45; 17,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,82</t>
+          <t>15,34; 18,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,14; 23,76</t>
+          <t>14,39; 23,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 20,73</t>
+          <t>16,76; 20,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,1; 31,5</t>
+          <t>27,47; 31,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 29,18</t>
+          <t>25,21; 29,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 55,92</t>
+          <t>32,29; 56,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,88; 16,31</t>
+          <t>14,0; 16,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,1; 24,04</t>
+          <t>21,13; 24,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 23,46</t>
+          <t>20,78; 23,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,28; 40,91</t>
+          <t>25,16; 40,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,38</t>
+          <t>9,15; 14,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,08</t>
+          <t>8,32; 14,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 21,86</t>
+          <t>15,11; 22,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 23,57</t>
+          <t>16,77; 23,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,08</t>
+          <t>15,76; 23,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 31,35</t>
+          <t>22,44; 31,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,2; 30,35</t>
+          <t>22,55; 30,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 32,91</t>
+          <t>26,81; 33,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 17,48</t>
+          <t>12,98; 17,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 21,43</t>
+          <t>15,98; 21,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,87</t>
+          <t>19,92; 25,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,81; 27,37</t>
+          <t>22,6; 27,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 15,25</t>
+          <t>12,82; 15,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 19,26</t>
+          <t>16,61; 19,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,22</t>
+          <t>17,46; 20,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 24,86</t>
+          <t>17,49; 24,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,42</t>
+          <t>22,43; 25,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 35,11</t>
+          <t>31,8; 35,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 32,84</t>
+          <t>29,5; 32,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,74; 54,32</t>
+          <t>37,71; 51,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,95</t>
+          <t>17,99; 19,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,73; 26,84</t>
+          <t>24,76; 26,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 26,23</t>
+          <t>24,1; 26,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 38,48</t>
+          <t>29,04; 38,51</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>168463; 215724</t>
+          <t>171450; 219999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>212128; 269387</t>
+          <t>214424; 269206</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160679; 205423</t>
+          <t>158165; 203600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158071; 197665</t>
+          <t>159057; 197394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>388106; 453879</t>
+          <t>390453; 454023</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>511849; 583391</t>
+          <t>507869; 583240</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>381947; 447259</t>
+          <t>381242; 450050</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>428449; 469970</t>
+          <t>428431; 470187</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>566979; 656377</t>
+          <t>568318; 654825</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>740158; 831530</t>
+          <t>738572; 834168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>554312; 631910</t>
+          <t>555733; 635322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>599865; 656546</t>
+          <t>595828; 655960</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174053; 227635</t>
+          <t>174258; 227950</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>282858; 351503</t>
+          <t>283316; 351248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>320787; 390673</t>
+          <t>318601; 388743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323806; 544106</t>
+          <t>329483; 541441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>267052; 329141</t>
+          <t>266050; 328419</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>475870; 553081</t>
+          <t>482262; 557171</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>501275; 580160</t>
+          <t>501243; 581821</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>718138; 1251007</t>
+          <t>722405; 1252702</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>455348; 534821</t>
+          <t>459096; 539443</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>784088; 893125</t>
+          <t>785243; 891759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>834564; 953608</t>
+          <t>844524; 948660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1144664; 1852083</t>
+          <t>1139236; 1821342</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50100; 79285</t>
+          <t>50456; 81638</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38429; 67626</t>
+          <t>39969; 67874</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82413; 119541</t>
+          <t>82656; 122234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106845; 152427</t>
+          <t>108457; 153057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74982; 109950</t>
+          <t>75098; 109608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104201; 143464</t>
+          <t>102678; 142552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>121889; 166685</t>
+          <t>123847; 166244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>174257; 217334</t>
+          <t>177093; 218189</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132347; 179694</t>
+          <t>133445; 179536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148702; 201051</t>
+          <t>149854; 198990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218302; 272565</t>
+          <t>218298; 276237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>298144; 357800</t>
+          <t>295392; 357009</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>419332; 499643</t>
+          <t>419788; 494030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>565558; 657445</t>
+          <t>567120; 658773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>590958; 682996</t>
+          <t>589847; 681730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>614117; 858275</t>
+          <t>603814; 856115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>760960; 859025</t>
+          <t>758119; 857376</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1127197; 1245441</t>
+          <t>1127773; 1249727</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1043301; 1160050</t>
+          <t>1042122; 1155131</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1377561; 1982829</t>
+          <t>1376471; 1877159</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1199751; 1327515</t>
+          <t>1197256; 1327501</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1721752; 1868573</t>
+          <t>1723524; 1877624</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1659162; 1812683</t>
+          <t>1665167; 1803398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2067673; 2733240</t>
+          <t>2062801; 2735279</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 21,32</t>
+          <t>16,23; 20,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,02; 27,64</t>
+          <t>21,78; 27,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,99</t>
+          <t>20,96; 27,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 38,33</t>
+          <t>29,35; 36,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,69; 34,52</t>
+          <t>29,2; 34,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 43,74</t>
+          <t>38,18; 43,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,33; 45,25</t>
+          <t>38,39; 45,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 62,47</t>
+          <t>56,37; 61,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,22; 27,9</t>
+          <t>24,28; 27,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,01; 36,15</t>
+          <t>31,95; 36,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 36,32</t>
+          <t>31,71; 36,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,01; 51,75</t>
+          <t>45,93; 50,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 13,47</t>
+          <t>10,17; 13,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,92</t>
+          <t>14,58; 18,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,34; 18,72</t>
+          <t>15,5; 19,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,39; 23,64</t>
+          <t>20,64; 24,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 20,69</t>
+          <t>16,68; 20,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,47; 31,73</t>
+          <t>27,35; 31,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 29,26</t>
+          <t>25,39; 29,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,29; 56,0</t>
+          <t>32,82; 36,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,0; 16,45</t>
+          <t>13,84; 16,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,0</t>
+          <t>21,07; 23,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,78; 23,34</t>
+          <t>20,75; 23,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,16; 40,23</t>
+          <t>27,29; 30,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,81</t>
+          <t>9,06; 14,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 14,13</t>
+          <t>8,15; 13,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 22,35</t>
+          <t>15,08; 22,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 23,67</t>
+          <t>16,79; 23,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 23,01</t>
+          <t>16,08; 23,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,44; 31,15</t>
+          <t>22,44; 31,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 30,27</t>
+          <t>22,69; 30,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,81; 33,04</t>
+          <t>26,45; 32,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 17,47</t>
+          <t>13,1; 17,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 21,21</t>
+          <t>16,06; 21,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 25,2</t>
+          <t>19,79; 24,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,6; 27,31</t>
+          <t>22,54; 26,88</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 15,08</t>
+          <t>12,79; 15,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,3</t>
+          <t>16,46; 19,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 20,18</t>
+          <t>17,47; 20,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,49; 24,8</t>
+          <t>22,37; 25,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,37</t>
+          <t>22,27; 25,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 35,23</t>
+          <t>31,82; 35,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,5; 32,7</t>
+          <t>29,65; 32,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,71; 51,43</t>
+          <t>37,56; 40,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,95</t>
+          <t>17,95; 19,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,76; 26,97</t>
+          <t>24,86; 26,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 26,1</t>
+          <t>24,07; 26,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 38,51</t>
+          <t>30,62; 32,65</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>191112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>449881</t>
+          <t>484423</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>626637</t>
+          <t>675535</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>171450; 219999</t>
+          <t>167467; 216545</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>214424; 269206</t>
+          <t>212062; 266478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>158165; 203600</t>
+          <t>158097; 203960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159057; 197394</t>
+          <t>169772; 213609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>390453; 454023</t>
+          <t>384019; 454743</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>507869; 583240</t>
+          <t>509085; 583849</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>381242; 450050</t>
+          <t>381802; 448276</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>428431; 470187</t>
+          <t>462647; 505399</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>568318; 654825</t>
+          <t>569882; 656119</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>738572; 834168</t>
+          <t>737272; 831048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>555733; 635322</t>
+          <t>554627; 635421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>595828; 655960</t>
+          <t>642682; 707289</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470523</t>
+          <t>505591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>884546</t>
+          <t>750939</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1355069</t>
+          <t>1256531</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174258; 227950</t>
+          <t>172069; 225699</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>283316; 351248</t>
+          <t>285831; 353911</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>318601; 388743</t>
+          <t>321862; 395888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>329483; 541441</t>
+          <t>460296; 551616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>266050; 328419</t>
+          <t>264843; 328028</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>482262; 557171</t>
+          <t>480197; 555837</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>501243; 581821</t>
+          <t>504744; 584866</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>722405; 1252702</t>
+          <t>712330; 792023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>459096; 539443</t>
+          <t>453849; 539451</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>785243; 891759</t>
+          <t>782829; 890856</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>844524; 948660</t>
+          <t>843533; 948453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1139236; 1821342</t>
+          <t>1201212; 1323888</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128330</t>
+          <t>141330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>196889</t>
+          <t>215854</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>325220</t>
+          <t>357184</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50456; 81638</t>
+          <t>49935; 78952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39969; 67874</t>
+          <t>39150; 66987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82656; 122234</t>
+          <t>82447; 120855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108457; 153057</t>
+          <t>119479; 166625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75098; 109608</t>
+          <t>76621; 109728</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>102678; 142552</t>
+          <t>102712; 142872</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>123847; 166244</t>
+          <t>124621; 167135</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>177093; 218189</t>
+          <t>194343; 239110</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>133445; 179536</t>
+          <t>134641; 179878</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149854; 198990</t>
+          <t>150642; 200843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218298; 276237</t>
+          <t>216915; 272383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>295392; 357009</t>
+          <t>326033; 388842</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>775610</t>
+          <t>838034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1531316</t>
+          <t>1451216</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2306926</t>
+          <t>2289249</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>419788; 494030</t>
+          <t>418796; 496828</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>567120; 658773</t>
+          <t>561817; 655811</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>589847; 681730</t>
+          <t>590081; 685276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>603814; 856115</t>
+          <t>787408; 892626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>758119; 857376</t>
+          <t>752583; 853098</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1127773; 1249727</t>
+          <t>1128738; 1246251</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1042122; 1155131</t>
+          <t>1047213; 1155565</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1376471; 1877159</t>
+          <t>1399468; 1502415</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1197256; 1327501</t>
+          <t>1194525; 1326086</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1723524; 1877624</t>
+          <t>1730663; 1877579</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1665167; 1803398</t>
+          <t>1663281; 1812302</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2062801; 2735279</t>
+          <t>2218670; 2366218</t>
         </is>
       </c>
     </row>
